--- a/compare/output/dscale_TFC_downscaled_SSP245.xlsx
+++ b/compare/output/dscale_TFC_downscaled_SSP245.xlsx
@@ -4478,58 +4478,58 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>2130126.682468</v>
+        <v>4025050.369155</v>
       </c>
       <c r="F54" t="n">
-        <v>2276570.524026</v>
+        <v>4298990.031007</v>
       </c>
       <c r="G54" t="n">
-        <v>2445860.205389</v>
+        <v>4597448.027859</v>
       </c>
       <c r="H54" t="n">
-        <v>2570425.856949</v>
+        <v>4799537.777662</v>
       </c>
       <c r="I54" t="n">
-        <v>2668908.375947</v>
+        <v>4944908.98219</v>
       </c>
       <c r="J54" t="n">
-        <v>2780394.908984</v>
+        <v>5108129.123931</v>
       </c>
       <c r="K54" t="n">
-        <v>3134475.960766</v>
+        <v>5283808.843897</v>
       </c>
       <c r="L54" t="n">
-        <v>3477124.284174</v>
+        <v>5465708.40489</v>
       </c>
       <c r="M54" t="n">
-        <v>3820044.329949</v>
+        <v>5667776.021016</v>
       </c>
       <c r="N54" t="n">
-        <v>4158038.30022</v>
+        <v>5878535.647727</v>
       </c>
       <c r="O54" t="n">
-        <v>4473134.048972</v>
+        <v>6074184.208993</v>
       </c>
       <c r="P54" t="n">
-        <v>4769975.79423</v>
+        <v>6260324.008031</v>
       </c>
       <c r="Q54" t="n">
-        <v>5052626.016904</v>
+        <v>6440455.093197</v>
       </c>
       <c r="R54" t="n">
-        <v>5296659.800922</v>
+        <v>6582280.046889</v>
       </c>
       <c r="S54" t="n">
-        <v>5501458.752119</v>
+        <v>6685709.518217</v>
       </c>
       <c r="T54" t="n">
-        <v>5666222.875895</v>
+        <v>6751526.028268</v>
       </c>
       <c r="U54" t="n">
-        <v>5789402.256668</v>
+        <v>6780125.487464</v>
       </c>
       <c r="V54" t="n">
-        <v>5880164.426836</v>
+        <v>6780776.275053</v>
       </c>
     </row>
     <row r="55">
@@ -4554,58 +4554,58 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>2592649.352332</v>
+        <v>697725.6656449999</v>
       </c>
       <c r="F55" t="n">
-        <v>2721555.941824</v>
+        <v>699136.434843</v>
       </c>
       <c r="G55" t="n">
-        <v>2864910.058786</v>
+        <v>713322.236316</v>
       </c>
       <c r="H55" t="n">
-        <v>2949460.660626</v>
+        <v>720348.739913</v>
       </c>
       <c r="I55" t="n">
-        <v>3001147.252518</v>
+        <v>725146.6462749999</v>
       </c>
       <c r="J55" t="n">
-        <v>3065192.802368</v>
+        <v>737458.587421</v>
       </c>
       <c r="K55" t="n">
-        <v>2904292.744412</v>
+        <v>754959.861282</v>
       </c>
       <c r="L55" t="n">
-        <v>2764099.039556</v>
+        <v>775514.9188409999</v>
       </c>
       <c r="M55" t="n">
-        <v>2647881.416225</v>
+        <v>800149.725158</v>
       </c>
       <c r="N55" t="n">
-        <v>2547554.344585</v>
+        <v>827056.997078</v>
       </c>
       <c r="O55" t="n">
-        <v>2454787.604623</v>
+        <v>853737.4446019999</v>
       </c>
       <c r="P55" t="n">
-        <v>2372017.142169</v>
+        <v>881668.928368</v>
       </c>
       <c r="Q55" t="n">
-        <v>2299524.253749</v>
+        <v>911695.177456</v>
       </c>
       <c r="R55" t="n">
-        <v>2224751.688336</v>
+        <v>939131.4423690001</v>
       </c>
       <c r="S55" t="n">
-        <v>2147666.936899</v>
+        <v>963416.170801</v>
       </c>
       <c r="T55" t="n">
-        <v>2069891.98042</v>
+        <v>984588.828047</v>
       </c>
       <c r="U55" t="n">
-        <v>1993509.708167</v>
+        <v>1002786.477371</v>
       </c>
       <c r="V55" t="n">
-        <v>1918910.19716</v>
+        <v>1018298.348943</v>
       </c>
     </row>
     <row r="56">
@@ -6910,58 +6910,58 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>911960.29797</v>
+        <v>466307.397713</v>
       </c>
       <c r="F86" t="n">
-        <v>967074.169378</v>
+        <v>483258.896432</v>
       </c>
       <c r="G86" t="n">
-        <v>1009520.625792</v>
+        <v>498364.361657</v>
       </c>
       <c r="H86" t="n">
-        <v>1024524.524428</v>
+        <v>506109.089829</v>
       </c>
       <c r="I86" t="n">
-        <v>1028651.18051</v>
+        <v>512894.462471</v>
       </c>
       <c r="J86" t="n">
-        <v>1029492.024615</v>
+        <v>519816.200256</v>
       </c>
       <c r="K86" t="n">
-        <v>1013329.376213</v>
+        <v>518135.203704</v>
       </c>
       <c r="L86" t="n">
-        <v>995044.490214</v>
+        <v>514546.72826</v>
       </c>
       <c r="M86" t="n">
-        <v>983965.6021660001</v>
+        <v>514089.103399</v>
       </c>
       <c r="N86" t="n">
-        <v>970073.058787</v>
+        <v>511855.670968</v>
       </c>
       <c r="O86" t="n">
-        <v>945319.503561</v>
+        <v>503576.815527</v>
       </c>
       <c r="P86" t="n">
-        <v>917463.853795</v>
+        <v>493367.82488</v>
       </c>
       <c r="Q86" t="n">
-        <v>892099.3654529999</v>
+        <v>484403.127844</v>
       </c>
       <c r="R86" t="n">
-        <v>865518.156001</v>
+        <v>474827.727905</v>
       </c>
       <c r="S86" t="n">
-        <v>841163.890898</v>
+        <v>466450.099928</v>
       </c>
       <c r="T86" t="n">
-        <v>818357.859049</v>
+        <v>458752.622536</v>
       </c>
       <c r="U86" t="n">
-        <v>795939.309676</v>
+        <v>450805.012064</v>
       </c>
       <c r="V86" t="n">
-        <v>774280.810048</v>
+        <v>442721.763443</v>
       </c>
     </row>
     <row r="87">
@@ -6986,58 +6986,58 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>133045.202918</v>
+        <v>68029.236019</v>
       </c>
       <c r="F87" t="n">
-        <v>158990.85982</v>
+        <v>79449.694648</v>
       </c>
       <c r="G87" t="n">
-        <v>190456.753976</v>
+        <v>94021.713072</v>
       </c>
       <c r="H87" t="n">
-        <v>216707.228407</v>
+        <v>107052.096376</v>
       </c>
       <c r="I87" t="n">
-        <v>238285.808686</v>
+        <v>118811.385313</v>
       </c>
       <c r="J87" t="n">
-        <v>256701.9154</v>
+        <v>129615.199605</v>
       </c>
       <c r="K87" t="n">
-        <v>268571.403036</v>
+        <v>137325.830956</v>
       </c>
       <c r="L87" t="n">
-        <v>277817.081254</v>
+        <v>143661.787608</v>
       </c>
       <c r="M87" t="n">
-        <v>287497.458145</v>
+        <v>150207.802145</v>
       </c>
       <c r="N87" t="n">
-        <v>295261.216001</v>
+        <v>155793.552308</v>
       </c>
       <c r="O87" t="n">
-        <v>298756.462197</v>
+        <v>159149.184254</v>
       </c>
       <c r="P87" t="n">
-        <v>300200.274328</v>
+        <v>161433.233321</v>
       </c>
       <c r="Q87" t="n">
-        <v>300181.456967</v>
+        <v>162996.233723</v>
       </c>
       <c r="R87" t="n">
-        <v>296855.165499</v>
+        <v>162856.276062</v>
       </c>
       <c r="S87" t="n">
-        <v>291506.031198</v>
+        <v>161648.661876</v>
       </c>
       <c r="T87" t="n">
-        <v>284699.252387</v>
+        <v>159595.862889</v>
       </c>
       <c r="U87" t="n">
-        <v>277019.112772</v>
+        <v>156898.400364</v>
       </c>
       <c r="V87" t="n">
-        <v>269262.218105</v>
+        <v>153959.961917</v>
       </c>
     </row>
     <row r="88">
@@ -7062,58 +7062,58 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>2326860.045618</v>
+        <v>1189779.922578</v>
       </c>
       <c r="F88" t="n">
-        <v>2213679.975328</v>
+        <v>1106203.201166</v>
       </c>
       <c r="G88" t="n">
-        <v>2134244.358925</v>
+        <v>1053600.392485</v>
       </c>
       <c r="H88" t="n">
-        <v>2100285.761912</v>
+        <v>1037528.814584</v>
       </c>
       <c r="I88" t="n">
-        <v>2112393.192824</v>
+        <v>1053257.694823</v>
       </c>
       <c r="J88" t="n">
-        <v>2157490.009954</v>
+        <v>1089370.516964</v>
       </c>
       <c r="K88" t="n">
-        <v>2183249.06292</v>
+        <v>1116338.107339</v>
       </c>
       <c r="L88" t="n">
-        <v>2204143.380722</v>
+        <v>1139782.970834</v>
       </c>
       <c r="M88" t="n">
-        <v>2239004.533171</v>
+        <v>1169804.950936</v>
       </c>
       <c r="N88" t="n">
-        <v>2269744.753872</v>
+        <v>1197622.914475</v>
       </c>
       <c r="O88" t="n">
-        <v>2279197.8656</v>
+        <v>1214141.03781</v>
       </c>
       <c r="P88" t="n">
-        <v>2283676.657497</v>
+        <v>1228051.198505</v>
       </c>
       <c r="Q88" t="n">
-        <v>2287457.872262</v>
+        <v>1242072.117799</v>
       </c>
       <c r="R88" t="n">
-        <v>2275959.373008</v>
+        <v>1248603.059793</v>
       </c>
       <c r="S88" t="n">
-        <v>2256637.819559</v>
+        <v>1251371.99519</v>
       </c>
       <c r="T88" t="n">
-        <v>2233424.024891</v>
+        <v>1252006.218702</v>
       </c>
       <c r="U88" t="n">
-        <v>2207941.722526</v>
+        <v>1250536.545638</v>
       </c>
       <c r="V88" t="n">
-        <v>2183386.725895</v>
+        <v>1248426.680632</v>
       </c>
     </row>
     <row r="89">
@@ -7138,58 +7138,58 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>260902.223697</v>
+        <v>133405.628798</v>
       </c>
       <c r="F89" t="n">
-        <v>263144.773428</v>
+        <v>131496.69057</v>
       </c>
       <c r="G89" t="n">
-        <v>273231.974547</v>
+        <v>134884.890017</v>
       </c>
       <c r="H89" t="n">
-        <v>277214.198352</v>
+        <v>136942.183686</v>
       </c>
       <c r="I89" t="n">
-        <v>278363.518311</v>
+        <v>138794.481357</v>
       </c>
       <c r="J89" t="n">
-        <v>278095.558865</v>
+        <v>140417.383779</v>
       </c>
       <c r="K89" t="n">
-        <v>272893.81945</v>
+        <v>139535.967327</v>
       </c>
       <c r="L89" t="n">
-        <v>266954.504075</v>
+        <v>138044.648272</v>
       </c>
       <c r="M89" t="n">
-        <v>263849.405735</v>
+        <v>137852.48603</v>
       </c>
       <c r="N89" t="n">
-        <v>261797.225077</v>
+        <v>138136.394043</v>
       </c>
       <c r="O89" t="n">
-        <v>259146.566676</v>
+        <v>138048.778545</v>
       </c>
       <c r="P89" t="n">
-        <v>257781.512889</v>
+        <v>138622.468648</v>
       </c>
       <c r="Q89" t="n">
-        <v>257760.85811</v>
+        <v>139962.173206</v>
       </c>
       <c r="R89" t="n">
-        <v>256906.115561</v>
+        <v>140940.021063</v>
       </c>
       <c r="S89" t="n">
-        <v>255839.252176</v>
+        <v>141870.384635</v>
       </c>
       <c r="T89" t="n">
-        <v>254630.503811</v>
+        <v>142740.012953</v>
       </c>
       <c r="U89" t="n">
-        <v>253221.129064</v>
+        <v>143419.671268</v>
       </c>
       <c r="V89" t="n">
-        <v>251986.26802</v>
+        <v>144081.841489</v>
       </c>
     </row>
     <row r="90">
@@ -7214,58 +7214,58 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>13883.388796</v>
+        <v>884267.915678</v>
       </c>
       <c r="F90" t="n">
-        <v>26052.258406</v>
+        <v>885884.349081</v>
       </c>
       <c r="G90" t="n">
-        <v>38090.049917</v>
+        <v>929153.793511</v>
       </c>
       <c r="H90" t="n">
-        <v>49662.749907</v>
+        <v>969701.724433</v>
       </c>
       <c r="I90" t="n">
-        <v>60868.54315</v>
+        <v>1005689.179847</v>
       </c>
       <c r="J90" t="n">
-        <v>71685.473178</v>
+        <v>1033860.583337</v>
       </c>
       <c r="K90" t="n">
-        <v>80813.316108</v>
+        <v>1038639.350744</v>
       </c>
       <c r="L90" t="n">
-        <v>89184.89379</v>
+        <v>1036721.735416</v>
       </c>
       <c r="M90" t="n">
-        <v>97749.325272</v>
+        <v>1041678.382027</v>
       </c>
       <c r="N90" t="n">
-        <v>105669.013297</v>
+        <v>1044185.132955</v>
       </c>
       <c r="O90" t="n">
-        <v>112023.723018</v>
+        <v>1036055.193302</v>
       </c>
       <c r="P90" t="n">
-        <v>117761.249298</v>
+        <v>1025714.459453</v>
       </c>
       <c r="Q90" t="n">
-        <v>123371.568461</v>
+        <v>1016546.705454</v>
       </c>
       <c r="R90" t="n">
-        <v>128232.028951</v>
+        <v>1003005.554808</v>
       </c>
       <c r="S90" t="n">
-        <v>132774.961093</v>
+        <v>988691.324091</v>
       </c>
       <c r="T90" t="n">
-        <v>137050.21079</v>
+        <v>973953.381455</v>
       </c>
       <c r="U90" t="n">
-        <v>141061.593869</v>
+        <v>958092.532519</v>
       </c>
       <c r="V90" t="n">
-        <v>145058.466139</v>
+        <v>942312.768781</v>
       </c>
     </row>
     <row r="91">
@@ -7290,58 +7290,58 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>539978.738821</v>
+        <v>276104.213177</v>
       </c>
       <c r="F91" t="n">
-        <v>571069.412624</v>
+        <v>285370.432661</v>
       </c>
       <c r="G91" t="n">
-        <v>600598.346743</v>
+        <v>296494.003233</v>
       </c>
       <c r="H91" t="n">
-        <v>603566.907948</v>
+        <v>298158.502944</v>
       </c>
       <c r="I91" t="n">
-        <v>590622.88329</v>
+        <v>294489.727896</v>
       </c>
       <c r="J91" t="n">
-        <v>570536.11271</v>
+        <v>288077.913308</v>
       </c>
       <c r="K91" t="n">
-        <v>540610.1048720001</v>
+        <v>276424.559859</v>
       </c>
       <c r="L91" t="n">
-        <v>511713.520173</v>
+        <v>264611.803996</v>
       </c>
       <c r="M91" t="n">
-        <v>489052.367956</v>
+        <v>255513.498444</v>
       </c>
       <c r="N91" t="n">
-        <v>469554.660262</v>
+        <v>247758.881155</v>
       </c>
       <c r="O91" t="n">
-        <v>451069.694236</v>
+        <v>240287.267266</v>
       </c>
       <c r="P91" t="n">
-        <v>436897.64601</v>
+        <v>234942.488922</v>
       </c>
       <c r="Q91" t="n">
-        <v>426615.058974</v>
+        <v>231648.711966</v>
       </c>
       <c r="R91" t="n">
-        <v>416363.081359</v>
+        <v>228418.935564</v>
       </c>
       <c r="S91" t="n">
-        <v>407346.956171</v>
+        <v>225885.859423</v>
       </c>
       <c r="T91" t="n">
-        <v>399902.792822</v>
+        <v>224176.322055</v>
       </c>
       <c r="U91" t="n">
-        <v>394172.327194</v>
+        <v>223251.771279</v>
       </c>
       <c r="V91" t="n">
-        <v>390607.841862</v>
+        <v>223343.508349</v>
       </c>
     </row>
     <row r="92">
@@ -7366,58 +7366,58 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>347839.903376</v>
+        <v>177858.970971</v>
       </c>
       <c r="F92" t="n">
-        <v>370688.305084</v>
+        <v>185237.520459</v>
       </c>
       <c r="G92" t="n">
-        <v>401945.620959</v>
+        <v>198426.230918</v>
       </c>
       <c r="H92" t="n">
-        <v>414846.688587</v>
+        <v>204931.824444</v>
       </c>
       <c r="I92" t="n">
-        <v>415476.514139</v>
+        <v>207160.218572</v>
       </c>
       <c r="J92" t="n">
-        <v>410129.814746</v>
+        <v>207084.772699</v>
       </c>
       <c r="K92" t="n">
-        <v>396047.252398</v>
+        <v>202506.735337</v>
       </c>
       <c r="L92" t="n">
-        <v>380270.557153</v>
+        <v>196641.429566</v>
       </c>
       <c r="M92" t="n">
-        <v>368721.397656</v>
+        <v>192644.592766</v>
       </c>
       <c r="N92" t="n">
-        <v>358708.541103</v>
+        <v>189271.312429</v>
       </c>
       <c r="O92" t="n">
-        <v>347783.269117</v>
+        <v>185266.029629</v>
       </c>
       <c r="P92" t="n">
-        <v>338454.808241</v>
+        <v>182004.67721</v>
       </c>
       <c r="Q92" t="n">
-        <v>330907.239926</v>
+        <v>179680.098713</v>
       </c>
       <c r="R92" t="n">
-        <v>322437.295502</v>
+        <v>176890.764628</v>
       </c>
       <c r="S92" t="n">
-        <v>314041.096678</v>
+        <v>174145.018006</v>
       </c>
       <c r="T92" t="n">
-        <v>305974.423417</v>
+        <v>171522.235192</v>
       </c>
       <c r="U92" t="n">
-        <v>298327.058541</v>
+        <v>168966.818939</v>
       </c>
       <c r="V92" t="n">
-        <v>291629.895638</v>
+        <v>166749.453162</v>
       </c>
     </row>
     <row r="93">
@@ -7442,58 +7442,58 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>43388.481256</v>
+        <v>22185.581796</v>
       </c>
       <c r="F93" t="n">
-        <v>48694.976569</v>
+        <v>24333.480703</v>
       </c>
       <c r="G93" t="n">
-        <v>56135.686189</v>
+        <v>27712.188042</v>
       </c>
       <c r="H93" t="n">
-        <v>63238.634799</v>
+        <v>31239.513684</v>
       </c>
       <c r="I93" t="n">
-        <v>69501.085117</v>
+        <v>34653.848037</v>
       </c>
       <c r="J93" t="n">
-        <v>74501.470739</v>
+        <v>37617.650751</v>
       </c>
       <c r="K93" t="n">
-        <v>76941.892227</v>
+        <v>39341.900016</v>
       </c>
       <c r="L93" t="n">
-        <v>78058.964724</v>
+        <v>40365.014133</v>
       </c>
       <c r="M93" t="n">
-        <v>78871.604838</v>
+        <v>41207.774465</v>
       </c>
       <c r="N93" t="n">
-        <v>78960.66782</v>
+        <v>41663.321377</v>
       </c>
       <c r="O93" t="n">
-        <v>78017.55517399999</v>
+        <v>41560.373865</v>
       </c>
       <c r="P93" t="n">
-        <v>76844.04133399999</v>
+        <v>41323.020379</v>
       </c>
       <c r="Q93" t="n">
-        <v>75633.93010500001</v>
+        <v>41068.64519</v>
       </c>
       <c r="R93" t="n">
-        <v>73857.881246</v>
+        <v>40518.814882</v>
       </c>
       <c r="S93" t="n">
-        <v>71775.53645499999</v>
+        <v>39801.6445</v>
       </c>
       <c r="T93" t="n">
-        <v>69504.7056</v>
+        <v>38962.741813</v>
       </c>
       <c r="U93" t="n">
-        <v>67187.166101</v>
+        <v>38053.543601</v>
       </c>
       <c r="V93" t="n">
-        <v>65064.450448</v>
+        <v>37202.844066</v>
       </c>
     </row>
     <row r="94">
@@ -7518,58 +7518,58 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>55316.12799</v>
+        <v>3120957.63373</v>
       </c>
       <c r="F94" t="n">
-        <v>106833.991052</v>
+        <v>3420487.858132</v>
       </c>
       <c r="G94" t="n">
-        <v>157683.948412</v>
+        <v>3650625.346176</v>
       </c>
       <c r="H94" t="n">
-        <v>205424.120912</v>
+        <v>3758982.607782</v>
       </c>
       <c r="I94" t="n">
-        <v>250141.782434</v>
+        <v>3803300.157412</v>
       </c>
       <c r="J94" t="n">
-        <v>292322.733057</v>
+        <v>3821196.088238</v>
       </c>
       <c r="K94" t="n">
-        <v>327289.50407</v>
+        <v>3769015.088236</v>
       </c>
       <c r="L94" t="n">
-        <v>359074.76276</v>
+        <v>3702211.505672</v>
       </c>
       <c r="M94" t="n">
-        <v>391138.447226</v>
+        <v>3657845.90387</v>
       </c>
       <c r="N94" t="n">
-        <v>419855.784281</v>
+        <v>3605124.443568</v>
       </c>
       <c r="O94" t="n">
-        <v>441860.82519</v>
+        <v>3522700.294014</v>
       </c>
       <c r="P94" t="n">
-        <v>460891.849467</v>
+        <v>3440579.41836</v>
       </c>
       <c r="Q94" t="n">
-        <v>478892.287334</v>
+        <v>3365339.052244</v>
       </c>
       <c r="R94" t="n">
-        <v>493589.617225</v>
+        <v>3274188.127855</v>
       </c>
       <c r="S94" t="n">
-        <v>507142.913582</v>
+        <v>3180035.273422</v>
       </c>
       <c r="T94" t="n">
-        <v>520202.592161</v>
+        <v>3088453.26834</v>
       </c>
       <c r="U94" t="n">
-        <v>533158.842311</v>
+        <v>3003766.352838</v>
       </c>
       <c r="V94" t="n">
-        <v>547045.07718</v>
+        <v>2931884.186444</v>
       </c>
     </row>
     <row r="95">
@@ -7594,58 +7594,58 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>2073835.014959</v>
+        <v>1060402.09345</v>
       </c>
       <c r="F95" t="n">
-        <v>2371541.961649</v>
+        <v>1185088.783796</v>
       </c>
       <c r="G95" t="n">
-        <v>2665318.879787</v>
+        <v>1315772.960157</v>
       </c>
       <c r="H95" t="n">
-        <v>2846649.597383</v>
+        <v>1406228.159934</v>
       </c>
       <c r="I95" t="n">
-        <v>2951596.753227</v>
+        <v>1471691.919341</v>
       </c>
       <c r="J95" t="n">
-        <v>2997687.564822</v>
+        <v>1513607.218166</v>
       </c>
       <c r="K95" t="n">
-        <v>2956315.996284</v>
+        <v>1511622.40719</v>
       </c>
       <c r="L95" t="n">
-        <v>2880426.411831</v>
+        <v>1489495.194215</v>
       </c>
       <c r="M95" t="n">
-        <v>2811267.844448</v>
+        <v>1468793.383006</v>
       </c>
       <c r="N95" t="n">
-        <v>2729075.752124</v>
+        <v>1439987.315978</v>
       </c>
       <c r="O95" t="n">
-        <v>2622774.130543</v>
+        <v>1397165.973548</v>
       </c>
       <c r="P95" t="n">
-        <v>2519772.277605</v>
+        <v>1355012.039605</v>
       </c>
       <c r="Q95" t="n">
-        <v>2427379.46822</v>
+        <v>1318048.473527</v>
       </c>
       <c r="R95" t="n">
-        <v>2331451.230252</v>
+        <v>1279046.179107</v>
       </c>
       <c r="S95" t="n">
-        <v>2241585.953853</v>
+        <v>1243025.29327</v>
       </c>
       <c r="T95" t="n">
-        <v>2160244.940793</v>
+        <v>1210983.704684</v>
       </c>
       <c r="U95" t="n">
-        <v>2086150.079596</v>
+        <v>1181556.056306</v>
       </c>
       <c r="V95" t="n">
-        <v>2022101.990705</v>
+        <v>1156206.569461</v>
       </c>
     </row>
     <row r="96">
@@ -7670,58 +7670,58 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>974903.939702</v>
+        <v>498492.006893</v>
       </c>
       <c r="F96" t="n">
-        <v>970994.1700789999</v>
+        <v>485217.769157</v>
       </c>
       <c r="G96" t="n">
-        <v>943733.553403</v>
+        <v>465887.628148</v>
       </c>
       <c r="H96" t="n">
-        <v>921496.822014</v>
+        <v>455214.010743</v>
       </c>
       <c r="I96" t="n">
-        <v>913057.867046</v>
+        <v>455258.626828</v>
       </c>
       <c r="J96" t="n">
-        <v>916614.4382260001</v>
+        <v>462821.491557</v>
       </c>
       <c r="K96" t="n">
-        <v>911367.544472</v>
+        <v>466000.117424</v>
       </c>
       <c r="L96" t="n">
-        <v>905091.411659</v>
+        <v>468031.157628</v>
       </c>
       <c r="M96" t="n">
-        <v>904548.715529</v>
+        <v>472596.43744</v>
       </c>
       <c r="N96" t="n">
-        <v>901753.034167</v>
+        <v>475806.847917</v>
       </c>
       <c r="O96" t="n">
-        <v>890717.483945</v>
+        <v>474490.024177</v>
       </c>
       <c r="P96" t="n">
-        <v>878817.720696</v>
+        <v>472585.79783</v>
       </c>
       <c r="Q96" t="n">
-        <v>868050.2351920001</v>
+        <v>471344.63417</v>
       </c>
       <c r="R96" t="n">
-        <v>852557.3119419999</v>
+        <v>467717.341954</v>
       </c>
       <c r="S96" t="n">
-        <v>835186.47439</v>
+        <v>463135.446794</v>
       </c>
       <c r="T96" t="n">
-        <v>816914.636943</v>
+        <v>457943.585366</v>
       </c>
       <c r="U96" t="n">
-        <v>798634.526508</v>
+        <v>452331.532041</v>
       </c>
       <c r="V96" t="n">
-        <v>782133.048339</v>
+        <v>447211.551563</v>
       </c>
     </row>
     <row r="97">
@@ -7746,58 +7746,58 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>441759.647657</v>
+        <v>225882.411956</v>
       </c>
       <c r="F97" t="n">
-        <v>406293.898022</v>
+        <v>203030.074634</v>
       </c>
       <c r="G97" t="n">
-        <v>383112.892876</v>
+        <v>189129.184112</v>
       </c>
       <c r="H97" t="n">
-        <v>372468.583599</v>
+        <v>183997.289807</v>
       </c>
       <c r="I97" t="n">
-        <v>373047.130476</v>
+        <v>186004.557315</v>
       </c>
       <c r="J97" t="n">
-        <v>380200.737436</v>
+        <v>191972.835091</v>
       </c>
       <c r="K97" t="n">
-        <v>383596.330738</v>
+        <v>196140.334656</v>
       </c>
       <c r="L97" t="n">
-        <v>385871.968569</v>
+        <v>199537.971325</v>
       </c>
       <c r="M97" t="n">
-        <v>390690.135701</v>
+        <v>204122.523315</v>
       </c>
       <c r="N97" t="n">
-        <v>395365.09671</v>
+        <v>208613.016329</v>
       </c>
       <c r="O97" t="n">
-        <v>397551.98843</v>
+        <v>211778.095751</v>
       </c>
       <c r="P97" t="n">
-        <v>400379.557723</v>
+        <v>215304.821768</v>
       </c>
       <c r="Q97" t="n">
-        <v>404283.454454</v>
+        <v>219522.821624</v>
       </c>
       <c r="R97" t="n">
-        <v>406042.629452</v>
+        <v>222757.082377</v>
       </c>
       <c r="S97" t="n">
-        <v>406446.825708</v>
+        <v>225386.710626</v>
       </c>
       <c r="T97" t="n">
-        <v>405495.451267</v>
+        <v>227311.437946</v>
       </c>
       <c r="U97" t="n">
-        <v>403269.746911</v>
+        <v>228404.378212</v>
       </c>
       <c r="V97" t="n">
-        <v>400602.817254</v>
+        <v>229058.480325</v>
       </c>
     </row>
     <row r="98">
@@ -7822,58 +7822,58 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>496941.981557</v>
+        <v>1272193.744094</v>
       </c>
       <c r="F98" t="n">
-        <v>498666.297269</v>
+        <v>1187181.729119</v>
       </c>
       <c r="G98" t="n">
-        <v>499436.563528</v>
+        <v>1080658.611102</v>
       </c>
       <c r="H98" t="n">
-        <v>495973.076958</v>
+        <v>990788.83424</v>
       </c>
       <c r="I98" t="n">
-        <v>495706.255023</v>
+        <v>934321.872283</v>
       </c>
       <c r="J98" t="n">
-        <v>499681.690232</v>
+        <v>906730.248078</v>
       </c>
       <c r="K98" t="n">
-        <v>546859.71074</v>
+        <v>890388.416313</v>
       </c>
       <c r="L98" t="n">
-        <v>588107.87367</v>
+        <v>881005.875444</v>
       </c>
       <c r="M98" t="n">
-        <v>627183.256921</v>
+        <v>879159.705176</v>
       </c>
       <c r="N98" t="n">
-        <v>661152.807026</v>
+        <v>877633.526966</v>
       </c>
       <c r="O98" t="n">
-        <v>688377.139322</v>
+        <v>873054.43402</v>
       </c>
       <c r="P98" t="n">
-        <v>711986.7110980001</v>
+        <v>868615.798691</v>
       </c>
       <c r="Q98" t="n">
-        <v>734627.008909</v>
+        <v>866774.294041</v>
       </c>
       <c r="R98" t="n">
-        <v>751112.1666849999</v>
+        <v>861122.0749069999</v>
       </c>
       <c r="S98" t="n">
-        <v>762838.23415</v>
+        <v>853058.251346</v>
       </c>
       <c r="T98" t="n">
-        <v>771027.410295</v>
+        <v>843163.657158</v>
       </c>
       <c r="U98" t="n">
-        <v>775451.865624</v>
+        <v>831509.952783</v>
       </c>
       <c r="V98" t="n">
-        <v>775779.142441</v>
+        <v>817879.951826</v>
       </c>
     </row>
     <row r="99">
@@ -7898,58 +7898,58 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>639261.091595</v>
+        <v>1925519.057981</v>
       </c>
       <c r="F99" t="n">
-        <v>650279.897</v>
+        <v>2063631.16684</v>
       </c>
       <c r="G99" t="n">
-        <v>660047.1738709999</v>
+        <v>2179925.225241</v>
       </c>
       <c r="H99" t="n">
-        <v>663665.288509</v>
+        <v>2235907.051358</v>
       </c>
       <c r="I99" t="n">
-        <v>671312.9440359999</v>
+        <v>2274111.323554</v>
       </c>
       <c r="J99" t="n">
-        <v>684433.56394</v>
+        <v>2310335.794017</v>
       </c>
       <c r="K99" t="n">
-        <v>756553.2185139999</v>
+        <v>2326786.667305</v>
       </c>
       <c r="L99" t="n">
-        <v>821500.340674</v>
+        <v>2332253.657829</v>
       </c>
       <c r="M99" t="n">
-        <v>885343.093962</v>
+        <v>2344584.64369</v>
       </c>
       <c r="N99" t="n">
-        <v>944607.186408</v>
+        <v>2354042.223341</v>
       </c>
       <c r="O99" t="n">
-        <v>997201.743022</v>
+        <v>2356229.263781</v>
       </c>
       <c r="P99" t="n">
-        <v>1046793.876505</v>
+        <v>2360102.495874</v>
       </c>
       <c r="Q99" t="n">
-        <v>1096597.058834</v>
+        <v>2371826.630294</v>
       </c>
       <c r="R99" t="n">
-        <v>1138730.16313</v>
+        <v>2373497.392165</v>
       </c>
       <c r="S99" t="n">
-        <v>1174960.762501</v>
+        <v>2369483.964181</v>
       </c>
       <c r="T99" t="n">
-        <v>1206849.135944</v>
+        <v>2362167.493598</v>
       </c>
       <c r="U99" t="n">
-        <v>1234246.220333</v>
+        <v>2351281.655832</v>
       </c>
       <c r="V99" t="n">
-        <v>1255218.903686</v>
+        <v>2333896.552127</v>
       </c>
     </row>
     <row r="100">
@@ -7974,58 +7974,58 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>327687.547268</v>
+        <v>638666.654688</v>
       </c>
       <c r="F100" t="n">
-        <v>330926.186009</v>
+        <v>595471.3106579999</v>
       </c>
       <c r="G100" t="n">
-        <v>334481.703101</v>
+        <v>553827.763605</v>
       </c>
       <c r="H100" t="n">
-        <v>335832.098148</v>
+        <v>520342.252171</v>
       </c>
       <c r="I100" t="n">
-        <v>339570.020086</v>
+        <v>502129.155227</v>
       </c>
       <c r="J100" t="n">
-        <v>346187.095304</v>
+        <v>497054.205972</v>
       </c>
       <c r="K100" t="n">
-        <v>383322.961868</v>
+        <v>497208.056761</v>
       </c>
       <c r="L100" t="n">
-        <v>417981.039972</v>
+        <v>501189.816907</v>
       </c>
       <c r="M100" t="n">
-        <v>453507.886825</v>
+        <v>510523.669369</v>
       </c>
       <c r="N100" t="n">
-        <v>487849.981742</v>
+        <v>521457.004884</v>
       </c>
       <c r="O100" t="n">
-        <v>519758.516117</v>
+        <v>532200.72982</v>
       </c>
       <c r="P100" t="n">
-        <v>550676.906092</v>
+        <v>544336.409497</v>
       </c>
       <c r="Q100" t="n">
-        <v>582223.934015</v>
+        <v>559133.123086</v>
       </c>
       <c r="R100" t="n">
-        <v>610423.607247</v>
+        <v>572252.893973</v>
       </c>
       <c r="S100" t="n">
-        <v>636275.034901</v>
+        <v>584389.788931</v>
       </c>
       <c r="T100" t="n">
-        <v>660605.996729</v>
+        <v>595976.912931</v>
       </c>
       <c r="U100" t="n">
-        <v>683372.903233</v>
+        <v>606857.938779</v>
       </c>
       <c r="V100" t="n">
-        <v>704657.483187</v>
+        <v>616980.113612</v>
       </c>
     </row>
     <row r="101">
@@ -8050,58 +8050,58 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>317188.893306</v>
+        <v>1139456.689261</v>
       </c>
       <c r="F101" t="n">
-        <v>321287.6775</v>
+        <v>1125068.720583</v>
       </c>
       <c r="G101" t="n">
-        <v>324656.825151</v>
+        <v>1095447.682616</v>
       </c>
       <c r="H101" t="n">
-        <v>324860.360753</v>
+        <v>1055902.564159</v>
       </c>
       <c r="I101" t="n">
-        <v>326757.395728</v>
+        <v>1027746.480898</v>
       </c>
       <c r="J101" t="n">
-        <v>331263.296977</v>
+        <v>1014728.550923</v>
       </c>
       <c r="K101" t="n">
-        <v>364892.167948</v>
+        <v>1005391.886711</v>
       </c>
       <c r="L101" t="n">
-        <v>396093.5266</v>
+        <v>1000395.813926</v>
       </c>
       <c r="M101" t="n">
-        <v>428069.004911</v>
+        <v>1004646.110132</v>
       </c>
       <c r="N101" t="n">
-        <v>458909.055849</v>
+        <v>1012272.723745</v>
       </c>
       <c r="O101" t="n">
-        <v>487531.330115</v>
+        <v>1020453.699451</v>
       </c>
       <c r="P101" t="n">
-        <v>515346.070948</v>
+        <v>1031906.875073</v>
       </c>
       <c r="Q101" t="n">
-        <v>543879.805222</v>
+        <v>1048303.343796</v>
       </c>
       <c r="R101" t="n">
-        <v>569218.635147</v>
+        <v>1060919.274816</v>
       </c>
       <c r="S101" t="n">
-        <v>592375.617282</v>
+        <v>1070910.274916</v>
       </c>
       <c r="T101" t="n">
-        <v>614154.950561</v>
+        <v>1079502.761438</v>
       </c>
       <c r="U101" t="n">
-        <v>634347.902202</v>
+        <v>1086985.280602</v>
       </c>
       <c r="V101" t="n">
-        <v>652343.100232</v>
+        <v>1092530.198567</v>
       </c>
     </row>
     <row r="102">
@@ -8126,58 +8126,58 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>3731076.60669</v>
+        <v>7311528.147128</v>
       </c>
       <c r="F102" t="n">
-        <v>3814071.380921</v>
+        <v>7698064.104456</v>
       </c>
       <c r="G102" t="n">
-        <v>3889742.335351</v>
+        <v>8056686.399626</v>
       </c>
       <c r="H102" t="n">
-        <v>3931223.066552</v>
+        <v>8285126.403398</v>
       </c>
       <c r="I102" t="n">
-        <v>3998156.072163</v>
+        <v>8519182.789966</v>
       </c>
       <c r="J102" t="n">
-        <v>4096444.490211</v>
+        <v>8785200.006727999</v>
       </c>
       <c r="K102" t="n">
-        <v>4547626.439632</v>
+        <v>8992003.792071</v>
       </c>
       <c r="L102" t="n">
-        <v>4956737.329749</v>
+        <v>9156771.380145</v>
       </c>
       <c r="M102" t="n">
-        <v>5363117.366981</v>
+        <v>9340194.127495</v>
       </c>
       <c r="N102" t="n">
-        <v>5747300.535388</v>
+        <v>9502032.149862999</v>
       </c>
       <c r="O102" t="n">
-        <v>6099826.226994</v>
+        <v>9629490.476885</v>
       </c>
       <c r="P102" t="n">
-        <v>6441405.536217</v>
+        <v>9764390.681446999</v>
       </c>
       <c r="Q102" t="n">
-        <v>6790704.569337</v>
+        <v>9935132.883345</v>
       </c>
       <c r="R102" t="n">
-        <v>7098089.228745</v>
+        <v>10066095.136073</v>
       </c>
       <c r="S102" t="n">
-        <v>7373884.020062</v>
+        <v>10174326.766372</v>
       </c>
       <c r="T102" t="n">
-        <v>7616028.145267</v>
+        <v>10258598.512792</v>
       </c>
       <c r="U102" t="n">
-        <v>7829492.221036</v>
+        <v>10316851.39493</v>
       </c>
       <c r="V102" t="n">
-        <v>8019157.472545</v>
+        <v>10352353.261955</v>
       </c>
     </row>
     <row r="103">
@@ -8202,58 +8202,58 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>4730596.614098</v>
+        <v>10419099.683743</v>
       </c>
       <c r="F103" t="n">
-        <v>4660136.444741</v>
+        <v>9396993.840632999</v>
       </c>
       <c r="G103" t="n">
-        <v>4583679.89711</v>
+        <v>8349741.809485</v>
       </c>
       <c r="H103" t="n">
-        <v>4475985.237652</v>
+        <v>7531380.350453</v>
       </c>
       <c r="I103" t="n">
-        <v>4405727.537537</v>
+        <v>7032476.546741</v>
       </c>
       <c r="J103" t="n">
-        <v>4377093.342719</v>
+        <v>6778408.477378</v>
       </c>
       <c r="K103" t="n">
-        <v>4721414.628221</v>
+        <v>6624732.172353</v>
       </c>
       <c r="L103" t="n">
-        <v>5006514.951611</v>
+        <v>6528988.134668</v>
       </c>
       <c r="M103" t="n">
-        <v>5271235.30478</v>
+        <v>6494391.730697</v>
       </c>
       <c r="N103" t="n">
-        <v>5499567.145977</v>
+        <v>6469800.630331</v>
       </c>
       <c r="O103" t="n">
-        <v>5683463.474918</v>
+        <v>6435984.364424</v>
       </c>
       <c r="P103" t="n">
-        <v>5848631.359702</v>
+        <v>6417919.766073</v>
       </c>
       <c r="Q103" t="n">
-        <v>6012287.32993</v>
+        <v>6430474.467806</v>
       </c>
       <c r="R103" t="n">
-        <v>6129868.705791</v>
+        <v>6422453.202986</v>
       </c>
       <c r="S103" t="n">
-        <v>6211757.917205</v>
+        <v>6397494.833633</v>
       </c>
       <c r="T103" t="n">
-        <v>6270319.277505</v>
+        <v>6359734.785577</v>
       </c>
       <c r="U103" t="n">
-        <v>6308680.11183</v>
+        <v>6310330.922287</v>
       </c>
       <c r="V103" t="n">
-        <v>6313728.492447</v>
+        <v>6247027.187595</v>
       </c>
     </row>
     <row r="104">
@@ -8278,58 +8278,58 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>4113806.015962</v>
+        <v>788643.5061699999</v>
       </c>
       <c r="F104" t="n">
-        <v>4099750.743852</v>
+        <v>810099.076994</v>
       </c>
       <c r="G104" t="n">
-        <v>4061095.892187</v>
+        <v>821178.6954570001</v>
       </c>
       <c r="H104" t="n">
-        <v>3993739.659649</v>
+        <v>829693.8613859999</v>
       </c>
       <c r="I104" t="n">
-        <v>3962299.505536</v>
+        <v>844680.54078</v>
       </c>
       <c r="J104" t="n">
-        <v>3967650.988142</v>
+        <v>865600.4672130001</v>
       </c>
       <c r="K104" t="n">
-        <v>3693443.178484</v>
+        <v>880541.554943</v>
       </c>
       <c r="L104" t="n">
-        <v>3443448.639489</v>
+        <v>888848.69007</v>
       </c>
       <c r="M104" t="n">
-        <v>3232664.058892</v>
+        <v>895876.69959</v>
       </c>
       <c r="N104" t="n">
-        <v>3039596.997741</v>
+        <v>897788.459766</v>
       </c>
       <c r="O104" t="n">
-        <v>2854191.918877</v>
+        <v>893081.851587</v>
       </c>
       <c r="P104" t="n">
-        <v>2686129.21206</v>
+        <v>886031.718326</v>
       </c>
       <c r="Q104" t="n">
-        <v>2540592.04654</v>
+        <v>879843.9529959999</v>
       </c>
       <c r="R104" t="n">
-        <v>2398333.905951</v>
+        <v>869332.9924540001</v>
       </c>
       <c r="S104" t="n">
-        <v>2264684.098338</v>
+        <v>857332.229308</v>
       </c>
       <c r="T104" t="n">
-        <v>2142742.461252</v>
+        <v>845805.619499</v>
       </c>
       <c r="U104" t="n">
-        <v>2029552.218205</v>
+        <v>834644.376164</v>
       </c>
       <c r="V104" t="n">
-        <v>1920493.2513</v>
+        <v>822419.296771</v>
       </c>
     </row>
     <row r="105">
@@ -8354,58 +8354,58 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>275781.189688</v>
+        <v>502426.03667</v>
       </c>
       <c r="F105" t="n">
-        <v>288495.628728</v>
+        <v>516496.455937</v>
       </c>
       <c r="G105" t="n">
-        <v>299619.376095</v>
+        <v>531406.956256</v>
       </c>
       <c r="H105" t="n">
-        <v>307330.631691</v>
+        <v>538030.659858</v>
       </c>
       <c r="I105" t="n">
-        <v>316903.36634</v>
+        <v>545785.169373</v>
       </c>
       <c r="J105" t="n">
-        <v>329242.882132</v>
+        <v>556110.291933</v>
       </c>
       <c r="K105" t="n">
-        <v>370623.876017</v>
+        <v>564591.677816</v>
       </c>
       <c r="L105" t="n">
-        <v>408978.867781</v>
+        <v>572620.03584</v>
       </c>
       <c r="M105" t="n">
-        <v>446726.062153</v>
+        <v>583932.9270809999</v>
       </c>
       <c r="N105" t="n">
-        <v>481823.954645</v>
+        <v>594915.219306</v>
       </c>
       <c r="O105" t="n">
-        <v>513136.365904</v>
+        <v>603356.664059</v>
       </c>
       <c r="P105" t="n">
-        <v>542576.384739</v>
+        <v>611034.052216</v>
       </c>
       <c r="Q105" t="n">
-        <v>571976.17686</v>
+        <v>619828.345368</v>
       </c>
       <c r="R105" t="n">
-        <v>597518.544812</v>
+        <v>625773.648426</v>
       </c>
       <c r="S105" t="n">
-        <v>620336.229683</v>
+        <v>630637.854697</v>
       </c>
       <c r="T105" t="n">
-        <v>641294.707584</v>
+        <v>635373.632895</v>
       </c>
       <c r="U105" t="n">
-        <v>660358.8505300001</v>
+        <v>639859.14844</v>
       </c>
       <c r="V105" t="n">
-        <v>677222.18872</v>
+        <v>643227.164915</v>
       </c>
     </row>
     <row r="106">
@@ -8430,58 +8430,58 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>3527097.348825</v>
+        <v>5647805.542101</v>
       </c>
       <c r="F106" t="n">
-        <v>3522007.281232</v>
+        <v>6012756.56488</v>
       </c>
       <c r="G106" t="n">
-        <v>3507285.316939</v>
+        <v>6401008.886076</v>
       </c>
       <c r="H106" t="n">
-        <v>3463441.398906</v>
+        <v>6617054.804355</v>
       </c>
       <c r="I106" t="n">
-        <v>3443749.145029</v>
+        <v>6768919.016203</v>
       </c>
       <c r="J106" t="n">
-        <v>3451093.237683</v>
+        <v>6893354.433112</v>
       </c>
       <c r="K106" t="n">
-        <v>3746202.196408</v>
+        <v>6932527.695931</v>
       </c>
       <c r="L106" t="n">
-        <v>3988591.525515</v>
+        <v>6906537.548846</v>
       </c>
       <c r="M106" t="n">
-        <v>4208347.421091</v>
+        <v>6875380.253932</v>
       </c>
       <c r="N106" t="n">
-        <v>4390947.54985</v>
+        <v>6814791.294294</v>
       </c>
       <c r="O106" t="n">
-        <v>4530941.191707</v>
+        <v>6717260.184737</v>
       </c>
       <c r="P106" t="n">
-        <v>4650354.798791</v>
+        <v>6615041.62791</v>
       </c>
       <c r="Q106" t="n">
-        <v>4768919.174756</v>
+        <v>6534245.737992</v>
       </c>
       <c r="R106" t="n">
-        <v>4857606.46609</v>
+        <v>6434728.400928</v>
       </c>
       <c r="S106" t="n">
-        <v>4927872.984932</v>
+        <v>6336170.572303</v>
       </c>
       <c r="T106" t="n">
-        <v>4980049.975235</v>
+        <v>6242568.016347</v>
       </c>
       <c r="U106" t="n">
-        <v>5009352.936993</v>
+        <v>6144787.948761</v>
       </c>
       <c r="V106" t="n">
-        <v>5018586.118682</v>
+        <v>6035672.491253</v>
       </c>
     </row>
     <row r="107">
@@ -8506,58 +8506,58 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>34069.767133</v>
+        <v>166836.591516</v>
       </c>
       <c r="F107" t="n">
-        <v>35889.035271</v>
+        <v>184712.368752</v>
       </c>
       <c r="G107" t="n">
-        <v>37841.091641</v>
+        <v>191574.103174</v>
       </c>
       <c r="H107" t="n">
-        <v>39531.654775</v>
+        <v>194164.409148</v>
       </c>
       <c r="I107" t="n">
-        <v>41494.310866</v>
+        <v>198548.250413</v>
       </c>
       <c r="J107" t="n">
-        <v>43799.67118</v>
+        <v>205919.04257</v>
       </c>
       <c r="K107" t="n">
-        <v>50013.369748</v>
+        <v>213623.848788</v>
       </c>
       <c r="L107" t="n">
-        <v>55957.673528</v>
+        <v>221210.079431</v>
       </c>
       <c r="M107" t="n">
-        <v>61964.45202</v>
+        <v>229304.302644</v>
       </c>
       <c r="N107" t="n">
-        <v>67716.782682</v>
+        <v>236326.086229</v>
       </c>
       <c r="O107" t="n">
-        <v>72917.51463999999</v>
+        <v>241455.865399</v>
       </c>
       <c r="P107" t="n">
-        <v>77722.203404</v>
+        <v>245430.744023</v>
       </c>
       <c r="Q107" t="n">
-        <v>82310.095892</v>
+        <v>248858.152388</v>
       </c>
       <c r="R107" t="n">
-        <v>86081.156538</v>
+        <v>249959.655878</v>
       </c>
       <c r="S107" t="n">
-        <v>89182.07307699999</v>
+        <v>249278.677191</v>
       </c>
       <c r="T107" t="n">
-        <v>91758.737953</v>
+        <v>247230.518159</v>
       </c>
       <c r="U107" t="n">
-        <v>93809.631051</v>
+        <v>244037.825409</v>
       </c>
       <c r="V107" t="n">
-        <v>95227.32668300001</v>
+        <v>239656.341843</v>
       </c>
     </row>
     <row r="108">
@@ -8582,58 +8582,58 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>991165.0919689999</v>
+        <v>2620089.447641</v>
       </c>
       <c r="F108" t="n">
-        <v>999692.936709</v>
+        <v>2641161.631031</v>
       </c>
       <c r="G108" t="n">
-        <v>1007128.107552</v>
+        <v>2589499.706025</v>
       </c>
       <c r="H108" t="n">
-        <v>1005778.905039</v>
+        <v>2509139.971165</v>
       </c>
       <c r="I108" t="n">
-        <v>1009748.691093</v>
+        <v>2454597.141869</v>
       </c>
       <c r="J108" t="n">
-        <v>1020826.773305</v>
+        <v>2435813.030892</v>
       </c>
       <c r="K108" t="n">
-        <v>1118888.333379</v>
+        <v>2422435.670247</v>
       </c>
       <c r="L108" t="n">
-        <v>1205956.501475</v>
+        <v>2415704.333285</v>
       </c>
       <c r="M108" t="n">
-        <v>1292272.396204</v>
+        <v>2426175.818132</v>
       </c>
       <c r="N108" t="n">
-        <v>1373256.469265</v>
+        <v>2439047.687603</v>
       </c>
       <c r="O108" t="n">
-        <v>1446956.497323</v>
+        <v>2448732.036099</v>
       </c>
       <c r="P108" t="n">
-        <v>1518197.352724</v>
+        <v>2464667.796309</v>
       </c>
       <c r="Q108" t="n">
-        <v>1591422.235941</v>
+        <v>2492874.509148</v>
       </c>
       <c r="R108" t="n">
-        <v>1654805.535394</v>
+        <v>2513245.240905</v>
       </c>
       <c r="S108" t="n">
-        <v>1710809.885341</v>
+        <v>2528502.028565</v>
       </c>
       <c r="T108" t="n">
-        <v>1761615.423454</v>
+        <v>2539154.324614</v>
       </c>
       <c r="U108" t="n">
-        <v>1807518.264071</v>
+        <v>2544068.64427</v>
       </c>
       <c r="V108" t="n">
-        <v>1845467.187997</v>
+        <v>2541138.212716</v>
       </c>
     </row>
     <row r="109">
@@ -8658,58 +8658,58 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>3832109.549437</v>
+        <v>777398.552903</v>
       </c>
       <c r="F109" t="n">
-        <v>3862348.942132</v>
+        <v>799461.096367</v>
       </c>
       <c r="G109" t="n">
-        <v>3871959.509828</v>
+        <v>845340.014206</v>
       </c>
       <c r="H109" t="n">
-        <v>3850928.911135</v>
+        <v>898498.712521</v>
       </c>
       <c r="I109" t="n">
-        <v>3859982.556815</v>
+        <v>963324.902128</v>
       </c>
       <c r="J109" t="n">
-        <v>3900530.493495</v>
+        <v>1029029.475666</v>
       </c>
       <c r="K109" t="n">
-        <v>3661744.24002</v>
+        <v>1079617.279184</v>
       </c>
       <c r="L109" t="n">
-        <v>3444856.156862</v>
+        <v>1115240.898775</v>
       </c>
       <c r="M109" t="n">
-        <v>3263862.809587</v>
+        <v>1143860.675792</v>
       </c>
       <c r="N109" t="n">
-        <v>3096664.450228</v>
+        <v>1162479.002679</v>
       </c>
       <c r="O109" t="n">
-        <v>2933444.006309</v>
+        <v>1170450.111853</v>
       </c>
       <c r="P109" t="n">
-        <v>2783458.151701</v>
+        <v>1173749.46828</v>
       </c>
       <c r="Q109" t="n">
-        <v>2652582.608211</v>
+        <v>1176763.500067</v>
       </c>
       <c r="R109" t="n">
-        <v>2521959.323878</v>
+        <v>1172308.332639</v>
       </c>
       <c r="S109" t="n">
-        <v>2397987.596534</v>
+        <v>1164441.515787</v>
       </c>
       <c r="T109" t="n">
-        <v>2283310.172361</v>
+        <v>1155720.810232</v>
       </c>
       <c r="U109" t="n">
-        <v>2176076.368131</v>
+        <v>1146493.470584</v>
       </c>
       <c r="V109" t="n">
-        <v>2072124.065702</v>
+        <v>1135154.07617</v>
       </c>
     </row>
     <row r="110">
@@ -8734,58 +8734,58 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>567979.577555</v>
+        <v>1516219.515796</v>
       </c>
       <c r="F110" t="n">
-        <v>587185.523737</v>
+        <v>1618237.380833</v>
       </c>
       <c r="G110" t="n">
-        <v>606100.514269</v>
+        <v>1712980.398768</v>
       </c>
       <c r="H110" t="n">
-        <v>617919.142492</v>
+        <v>1761798.843853</v>
       </c>
       <c r="I110" t="n">
-        <v>632563.550545</v>
+        <v>1795496.830456</v>
       </c>
       <c r="J110" t="n">
-        <v>653546.043364</v>
+        <v>1832213.775401</v>
       </c>
       <c r="K110" t="n">
-        <v>734478.485588</v>
+        <v>1860498.065202</v>
       </c>
       <c r="L110" t="n">
-        <v>813057.318468</v>
+        <v>1887874.089857</v>
       </c>
       <c r="M110" t="n">
-        <v>894179.978703</v>
+        <v>1927778.863508</v>
       </c>
       <c r="N110" t="n">
-        <v>972869.382289</v>
+        <v>1970590.314327</v>
       </c>
       <c r="O110" t="n">
-        <v>1045679.382493</v>
+        <v>2009410.619393</v>
       </c>
       <c r="P110" t="n">
-        <v>1116473.594372</v>
+        <v>2049525.229889</v>
       </c>
       <c r="Q110" t="n">
-        <v>1189135.419622</v>
+        <v>2095153.982064</v>
       </c>
       <c r="R110" t="n">
-        <v>1254972.984917</v>
+        <v>2130234.166387</v>
       </c>
       <c r="S110" t="n">
-        <v>1314895.857914</v>
+        <v>2158490.096237</v>
       </c>
       <c r="T110" t="n">
-        <v>1369896.582028</v>
+        <v>2182416.955488</v>
       </c>
       <c r="U110" t="n">
-        <v>1419742.274875</v>
+        <v>2201350.76549</v>
       </c>
       <c r="V110" t="n">
-        <v>1463350.111423</v>
+        <v>2213603.903995</v>
       </c>
     </row>
     <row r="111">
@@ -8810,58 +8810,58 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>17185887.385568</v>
+        <v>3826730.408085</v>
       </c>
       <c r="F111" t="n">
-        <v>17503969.974643</v>
+        <v>4029348.017604</v>
       </c>
       <c r="G111" t="n">
-        <v>17653803.402481</v>
+        <v>4147683.935106</v>
       </c>
       <c r="H111" t="n">
-        <v>17622284.528962</v>
+        <v>4182038.142681</v>
       </c>
       <c r="I111" t="n">
-        <v>17740575.702864</v>
+        <v>4237091.524782</v>
       </c>
       <c r="J111" t="n">
-        <v>18038036.989617</v>
+        <v>4327553.625176</v>
       </c>
       <c r="K111" t="n">
-        <v>17043528.037451</v>
+        <v>4397801.817454</v>
       </c>
       <c r="L111" t="n">
-        <v>16110791.344487</v>
+        <v>4445545.186062</v>
       </c>
       <c r="M111" t="n">
-        <v>15304893.645236</v>
+        <v>4499507.696488</v>
       </c>
       <c r="N111" t="n">
-        <v>14530069.008475</v>
+        <v>4534683.13977</v>
       </c>
       <c r="O111" t="n">
-        <v>13758023.714823</v>
+        <v>4537648.816242</v>
       </c>
       <c r="P111" t="n">
-        <v>13050854.858653</v>
+        <v>4525033.862274</v>
       </c>
       <c r="Q111" t="n">
-        <v>12440619.371915</v>
+        <v>4512405.715497</v>
       </c>
       <c r="R111" t="n">
-        <v>11831439.502812</v>
+        <v>4473225.70158</v>
       </c>
       <c r="S111" t="n">
-        <v>11252406.665135</v>
+        <v>4424894.981355</v>
       </c>
       <c r="T111" t="n">
-        <v>10706050.79801</v>
+        <v>4377410.942479</v>
       </c>
       <c r="U111" t="n">
-        <v>10181489.393899</v>
+        <v>4330051.730898</v>
       </c>
       <c r="V111" t="n">
-        <v>9677374.630168</v>
+        <v>4276692.562393</v>
       </c>
     </row>
     <row r="112">
@@ -8886,58 +8886,58 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>3717467.524149</v>
+        <v>5935502.607025</v>
       </c>
       <c r="F112" t="n">
-        <v>3806066.221833</v>
+        <v>6302090.706888</v>
       </c>
       <c r="G112" t="n">
-        <v>3887931.139841</v>
+        <v>6667848.662201</v>
       </c>
       <c r="H112" t="n">
-        <v>3931535.796107</v>
+        <v>6910162.896581</v>
       </c>
       <c r="I112" t="n">
-        <v>3997425.936189</v>
+        <v>7143561.445176</v>
       </c>
       <c r="J112" t="n">
-        <v>4096866.057002</v>
+        <v>7398645.190244</v>
       </c>
       <c r="K112" t="n">
-        <v>4557731.663433</v>
+        <v>7609173.906371</v>
       </c>
       <c r="L112" t="n">
-        <v>4983898.598333</v>
+        <v>7788286.147128</v>
       </c>
       <c r="M112" t="n">
-        <v>5409124.012826</v>
+        <v>7987173.527364</v>
       </c>
       <c r="N112" t="n">
-        <v>5809269.775186</v>
+        <v>8173741.619644</v>
       </c>
       <c r="O112" t="n">
-        <v>6173476.410851</v>
+        <v>8336116.315665</v>
       </c>
       <c r="P112" t="n">
-        <v>6524813.923231</v>
+        <v>8507634.414354</v>
       </c>
       <c r="Q112" t="n">
-        <v>6884457.870018</v>
+        <v>8710716.068112999</v>
       </c>
       <c r="R112" t="n">
-        <v>7202530.908123</v>
+        <v>8877542.721142</v>
       </c>
       <c r="S112" t="n">
-        <v>7489123.079432</v>
+        <v>9019978.221666001</v>
       </c>
       <c r="T112" t="n">
-        <v>7755228.071488</v>
+        <v>9146106.902458999</v>
       </c>
       <c r="U112" t="n">
-        <v>8003626.216869</v>
+        <v>9258006.323652999</v>
       </c>
       <c r="V112" t="n">
-        <v>8232196.829178</v>
+        <v>9354694.988655001</v>
       </c>
     </row>
     <row r="113">
@@ -9190,58 +9190,58 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>445201.502821</v>
+        <v>92163.600513</v>
       </c>
       <c r="F116" t="n">
-        <v>447516.633862</v>
+        <v>99788.86838699999</v>
       </c>
       <c r="G116" t="n">
-        <v>460391.408798</v>
+        <v>107120.867465</v>
       </c>
       <c r="H116" t="n">
-        <v>473010.160464</v>
+        <v>112168.688628</v>
       </c>
       <c r="I116" t="n">
-        <v>489785.366686</v>
+        <v>116239.908218</v>
       </c>
       <c r="J116" t="n">
-        <v>491757.917362</v>
+        <v>115575.451793</v>
       </c>
       <c r="K116" t="n">
-        <v>505659.631893</v>
+        <v>117078.350788</v>
       </c>
       <c r="L116" t="n">
-        <v>517406.217949</v>
+        <v>117971.828221</v>
       </c>
       <c r="M116" t="n">
-        <v>530011.932894</v>
+        <v>119278.978255</v>
       </c>
       <c r="N116" t="n">
-        <v>544061.919056</v>
+        <v>119749.36162</v>
       </c>
       <c r="O116" t="n">
-        <v>553020.7227320001</v>
+        <v>118652.365682</v>
       </c>
       <c r="P116" t="n">
-        <v>557530.770389</v>
+        <v>116959.044615</v>
       </c>
       <c r="Q116" t="n">
-        <v>559121.495301</v>
+        <v>115316.920181</v>
       </c>
       <c r="R116" t="n">
-        <v>554878.248511</v>
+        <v>112901.520751</v>
       </c>
       <c r="S116" t="n">
-        <v>547099.000126</v>
+        <v>110078.662002</v>
       </c>
       <c r="T116" t="n">
-        <v>536669.761836</v>
+        <v>107049.325992</v>
       </c>
       <c r="U116" t="n">
-        <v>524148.830146</v>
+        <v>103937.292718</v>
       </c>
       <c r="V116" t="n">
-        <v>510943.992471</v>
+        <v>101027.580624</v>
       </c>
     </row>
     <row r="117">
@@ -9266,58 +9266,58 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>740003.281693</v>
+        <v>153192.130755</v>
       </c>
       <c r="F117" t="n">
-        <v>895631.661142</v>
+        <v>199711.16869</v>
       </c>
       <c r="G117" t="n">
-        <v>986451.979707</v>
+        <v>229521.206867</v>
       </c>
       <c r="H117" t="n">
-        <v>1037007.721406</v>
+        <v>245913.948431</v>
       </c>
       <c r="I117" t="n">
-        <v>1072509.217182</v>
+        <v>254536.744966</v>
       </c>
       <c r="J117" t="n">
-        <v>1061828.14948</v>
+        <v>249556.262889</v>
       </c>
       <c r="K117" t="n">
-        <v>1069200.807868</v>
+        <v>247558.356158</v>
       </c>
       <c r="L117" t="n">
-        <v>1068123.680396</v>
+        <v>243538.826884</v>
       </c>
       <c r="M117" t="n">
-        <v>1064164.314207</v>
+        <v>239489.762807</v>
       </c>
       <c r="N117" t="n">
-        <v>1046314.156991</v>
+        <v>230296.30997</v>
       </c>
       <c r="O117" t="n">
-        <v>1014485.503538</v>
+        <v>217661.111052</v>
       </c>
       <c r="P117" t="n">
-        <v>980906.112615</v>
+        <v>205774.905856</v>
       </c>
       <c r="Q117" t="n">
-        <v>952018.234116</v>
+        <v>196350.545698</v>
       </c>
       <c r="R117" t="n">
-        <v>920335.007298</v>
+        <v>187261.29958</v>
       </c>
       <c r="S117" t="n">
-        <v>888009.492342</v>
+        <v>178671.313125</v>
       </c>
       <c r="T117" t="n">
-        <v>856292.058026</v>
+        <v>170804.271421</v>
       </c>
       <c r="U117" t="n">
-        <v>825567.909978</v>
+        <v>163707.879486</v>
       </c>
       <c r="V117" t="n">
-        <v>797701.9539880001</v>
+        <v>157727.460657</v>
       </c>
     </row>
     <row r="118">
@@ -9342,58 +9342,58 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>1524587.548871</v>
+        <v>315613.21539</v>
       </c>
       <c r="F118" t="n">
-        <v>1462306.581954</v>
+        <v>326070.38042</v>
       </c>
       <c r="G118" t="n">
-        <v>1421577.728109</v>
+        <v>330763.425411</v>
       </c>
       <c r="H118" t="n">
-        <v>1389776.494206</v>
+        <v>329568.83355</v>
       </c>
       <c r="I118" t="n">
-        <v>1381991.302513</v>
+        <v>327985.58938</v>
       </c>
       <c r="J118" t="n">
-        <v>1342006.531314</v>
+        <v>315405.214009</v>
       </c>
       <c r="K118" t="n">
-        <v>1340885.53034</v>
+        <v>310463.119036</v>
       </c>
       <c r="L118" t="n">
-        <v>1337904.661481</v>
+        <v>305050.564574</v>
       </c>
       <c r="M118" t="n">
-        <v>1340726.154997</v>
+        <v>301729.896937</v>
       </c>
       <c r="N118" t="n">
-        <v>1333759.764442</v>
+        <v>293563.792562</v>
       </c>
       <c r="O118" t="n">
-        <v>1313623.569601</v>
+        <v>281842.140342</v>
       </c>
       <c r="P118" t="n">
-        <v>1292582.471605</v>
+        <v>271158.50639</v>
       </c>
       <c r="Q118" t="n">
-        <v>1277303.377917</v>
+        <v>263439.508078</v>
       </c>
       <c r="R118" t="n">
-        <v>1256575.247355</v>
+        <v>255676.369988</v>
       </c>
       <c r="S118" t="n">
-        <v>1232390.944902</v>
+        <v>247962.336335</v>
       </c>
       <c r="T118" t="n">
-        <v>1205776.706082</v>
+        <v>240515.849526</v>
       </c>
       <c r="U118" t="n">
-        <v>1176916.149685</v>
+        <v>233379.283362</v>
       </c>
       <c r="V118" t="n">
-        <v>1147775.881759</v>
+        <v>226946.636307</v>
       </c>
     </row>
     <row r="119">
@@ -9418,58 +9418,58 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>415071.756959</v>
+        <v>85926.276866</v>
       </c>
       <c r="F119" t="n">
-        <v>480881.356861</v>
+        <v>107228.654308</v>
       </c>
       <c r="G119" t="n">
-        <v>556357.852969</v>
+        <v>129449.713205</v>
       </c>
       <c r="H119" t="n">
-        <v>623180.38075</v>
+        <v>147779.755976</v>
       </c>
       <c r="I119" t="n">
-        <v>683546.390708</v>
+        <v>162224.874655</v>
       </c>
       <c r="J119" t="n">
-        <v>712491.088122</v>
+        <v>167453.286467</v>
       </c>
       <c r="K119" t="n">
-        <v>750441.852139</v>
+        <v>173754.218983</v>
       </c>
       <c r="L119" t="n">
-        <v>781189.219686</v>
+        <v>178115.989402</v>
       </c>
       <c r="M119" t="n">
-        <v>810433.060881</v>
+        <v>182387.643459</v>
       </c>
       <c r="N119" t="n">
-        <v>830257.173339</v>
+        <v>182741.638416</v>
       </c>
       <c r="O119" t="n">
-        <v>837357.214991</v>
+        <v>179657.669949</v>
       </c>
       <c r="P119" t="n">
-        <v>839005.848706</v>
+        <v>176007.00751</v>
       </c>
       <c r="Q119" t="n">
-        <v>839976.535884</v>
+        <v>173242.323817</v>
       </c>
       <c r="R119" t="n">
-        <v>833786.064503</v>
+        <v>169651.117008</v>
       </c>
       <c r="S119" t="n">
-        <v>822318.6949389999</v>
+        <v>165454.04334</v>
       </c>
       <c r="T119" t="n">
-        <v>806635.965919</v>
+        <v>160899.388438</v>
       </c>
       <c r="U119" t="n">
-        <v>787123.808461</v>
+        <v>156084.518328</v>
       </c>
       <c r="V119" t="n">
-        <v>765340.6999839999</v>
+        <v>151328.756991</v>
       </c>
     </row>
     <row r="120">
@@ -9494,58 +9494,58 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>150559.581898</v>
+        <v>31168.163341</v>
       </c>
       <c r="F120" t="n">
-        <v>152043.51298</v>
+        <v>33903.209306</v>
       </c>
       <c r="G120" t="n">
-        <v>157406.046602</v>
+        <v>36624.211343</v>
       </c>
       <c r="H120" t="n">
-        <v>163047.9272</v>
+        <v>38664.861152</v>
       </c>
       <c r="I120" t="n">
-        <v>170611.328011</v>
+        <v>40490.889393</v>
       </c>
       <c r="J120" t="n">
-        <v>173500.198634</v>
+        <v>40776.90086</v>
       </c>
       <c r="K120" t="n">
-        <v>180977.505755</v>
+        <v>41902.787107</v>
       </c>
       <c r="L120" t="n">
-        <v>188092.590493</v>
+        <v>42886.277755</v>
       </c>
       <c r="M120" t="n">
-        <v>195902.58202</v>
+        <v>44087.799483</v>
       </c>
       <c r="N120" t="n">
-        <v>204623.741124</v>
+        <v>45038.186856</v>
       </c>
       <c r="O120" t="n">
-        <v>211348.273234</v>
+        <v>45345.448319</v>
       </c>
       <c r="P120" t="n">
-        <v>216307.786183</v>
+        <v>45377.140345</v>
       </c>
       <c r="Q120" t="n">
-        <v>220100.573057</v>
+        <v>45394.999885</v>
       </c>
       <c r="R120" t="n">
-        <v>221519.877796</v>
+        <v>45072.826601</v>
       </c>
       <c r="S120" t="n">
-        <v>221344.186002</v>
+        <v>44535.398221</v>
       </c>
       <c r="T120" t="n">
-        <v>219686.608745</v>
+        <v>43820.809496</v>
       </c>
       <c r="U120" t="n">
-        <v>216572.366685</v>
+        <v>42945.713462</v>
       </c>
       <c r="V120" t="n">
-        <v>212385.045267</v>
+        <v>41994.323449</v>
       </c>
     </row>
     <row r="121">
@@ -9570,58 +9570,58 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>1854917.732325</v>
+        <v>383996.675177</v>
       </c>
       <c r="F121" t="n">
-        <v>2123141.612091</v>
+        <v>473425.751948</v>
       </c>
       <c r="G121" t="n">
-        <v>2419361.2821</v>
+        <v>562921.189008</v>
       </c>
       <c r="H121" t="n">
-        <v>2641615.256994</v>
+        <v>626427.387832</v>
       </c>
       <c r="I121" t="n">
-        <v>2806140.32365</v>
+        <v>665976.396713</v>
       </c>
       <c r="J121" t="n">
-        <v>2828351.226647</v>
+        <v>664733.5188899999</v>
       </c>
       <c r="K121" t="n">
-        <v>2883792.563995</v>
+        <v>667701.465795</v>
       </c>
       <c r="L121" t="n">
-        <v>2913864.080226</v>
+        <v>664379.0909449999</v>
       </c>
       <c r="M121" t="n">
-        <v>2952600.406073</v>
+        <v>664481.566874</v>
       </c>
       <c r="N121" t="n">
-        <v>2968461.898791</v>
+        <v>653365.738206</v>
       </c>
       <c r="O121" t="n">
-        <v>2948599.598804</v>
+        <v>632631.479193</v>
       </c>
       <c r="P121" t="n">
-        <v>2916106.426502</v>
+        <v>611742.059369</v>
       </c>
       <c r="Q121" t="n">
-        <v>2886873.305969</v>
+        <v>595407.870013</v>
       </c>
       <c r="R121" t="n">
-        <v>2838805.088497</v>
+        <v>577613.940478</v>
       </c>
       <c r="S121" t="n">
-        <v>2779806.15966</v>
+        <v>559308.904986</v>
       </c>
       <c r="T121" t="n">
-        <v>2713369.733647</v>
+        <v>541234.893057</v>
       </c>
       <c r="U121" t="n">
-        <v>2638868.677755</v>
+        <v>523280.508187</v>
       </c>
       <c r="V121" t="n">
-        <v>2560117.345788</v>
+        <v>506205.113221</v>
       </c>
     </row>
     <row r="122">
@@ -9646,58 +9646,58 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>159493.460643</v>
+        <v>4227774.803168</v>
       </c>
       <c r="F122" t="n">
-        <v>301072.456885</v>
+        <v>4622465.782715</v>
       </c>
       <c r="G122" t="n">
-        <v>440144.795923</v>
+        <v>5045290.480909</v>
       </c>
       <c r="H122" t="n">
-        <v>580960.191302</v>
+        <v>5408074.656753</v>
       </c>
       <c r="I122" t="n">
-        <v>733671.970094</v>
+        <v>5770801.495517</v>
       </c>
       <c r="J122" t="n">
-        <v>870044.74107</v>
+        <v>5926479.217721</v>
       </c>
       <c r="K122" t="n">
-        <v>1032048.400545</v>
+        <v>6204547.994668</v>
       </c>
       <c r="L122" t="n">
-        <v>1197395.324246</v>
+        <v>6452033.196696</v>
       </c>
       <c r="M122" t="n">
-        <v>1369535.541199</v>
+        <v>6711918.344456</v>
       </c>
       <c r="N122" t="n">
-        <v>1535356.054674</v>
+        <v>6938079.680787</v>
       </c>
       <c r="O122" t="n">
-        <v>1684980.900139</v>
+        <v>7087625.568503</v>
       </c>
       <c r="P122" t="n">
-        <v>1828322.378181</v>
+        <v>7203743.130098</v>
       </c>
       <c r="Q122" t="n">
-        <v>1975081.529701</v>
+        <v>7321322.884273</v>
       </c>
       <c r="R122" t="n">
-        <v>2111495.373348</v>
+        <v>7389217.832901</v>
       </c>
       <c r="S122" t="n">
-        <v>2241663.626625</v>
+        <v>7426621.446588</v>
       </c>
       <c r="T122" t="n">
-        <v>2368518.56437</v>
+        <v>7442624.860695</v>
       </c>
       <c r="U122" t="n">
-        <v>2491094.354092</v>
+        <v>7436956.90126</v>
       </c>
       <c r="V122" t="n">
-        <v>2612576.111911</v>
+        <v>7421611.159918</v>
       </c>
     </row>
     <row r="123">
@@ -9722,58 +9722,58 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>77349.72663200001</v>
+        <v>147323.705233</v>
       </c>
       <c r="F123" t="n">
-        <v>81232.01719499999</v>
+        <v>152127.032248</v>
       </c>
       <c r="G123" t="n">
-        <v>86324.82749700001</v>
+        <v>163736.336605</v>
       </c>
       <c r="H123" t="n">
-        <v>89742.212862</v>
+        <v>171583.05954</v>
       </c>
       <c r="I123" t="n">
-        <v>92782.636048</v>
+        <v>178614.488229</v>
       </c>
       <c r="J123" t="n">
-        <v>96562.26366500001</v>
+        <v>186594.017361</v>
       </c>
       <c r="K123" t="n">
-        <v>100690.637761</v>
+        <v>194942.170452</v>
       </c>
       <c r="L123" t="n">
-        <v>104456.484892</v>
+        <v>202512.044851</v>
       </c>
       <c r="M123" t="n">
-        <v>108379.116526</v>
+        <v>210630.259829</v>
       </c>
       <c r="N123" t="n">
-        <v>112026.190087</v>
+        <v>218489.756041</v>
       </c>
       <c r="O123" t="n">
-        <v>114806.59167</v>
+        <v>224693.38644</v>
       </c>
       <c r="P123" t="n">
-        <v>117237.793171</v>
+        <v>229934.006327</v>
       </c>
       <c r="Q123" t="n">
-        <v>119598.359608</v>
+        <v>234562.3691</v>
       </c>
       <c r="R123" t="n">
-        <v>121415.004526</v>
+        <v>237634.184652</v>
       </c>
       <c r="S123" t="n">
-        <v>122747.061847</v>
+        <v>239346.452206</v>
       </c>
       <c r="T123" t="n">
-        <v>123663.019871</v>
+        <v>239798.914613</v>
       </c>
       <c r="U123" t="n">
-        <v>124056.268869</v>
+        <v>238997.009501</v>
       </c>
       <c r="V123" t="n">
-        <v>124096.304091</v>
+        <v>237135.928525</v>
       </c>
     </row>
     <row r="124">
@@ -9798,58 +9798,58 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>817378.719735</v>
+        <v>1051730.605553</v>
       </c>
       <c r="F124" t="n">
-        <v>843377.113874</v>
+        <v>1097805.206467</v>
       </c>
       <c r="G124" t="n">
-        <v>888202.369698</v>
+        <v>1171612.183648</v>
       </c>
       <c r="H124" t="n">
-        <v>919536.776145</v>
+        <v>1218849.419564</v>
       </c>
       <c r="I124" t="n">
-        <v>948065.501846</v>
+        <v>1253186.024742</v>
       </c>
       <c r="J124" t="n">
-        <v>983204.631611</v>
+        <v>1289096.374515</v>
       </c>
       <c r="K124" t="n">
-        <v>1021983.590511</v>
+        <v>1325138.321574</v>
       </c>
       <c r="L124" t="n">
-        <v>1059019.355085</v>
+        <v>1356219.442994</v>
       </c>
       <c r="M124" t="n">
-        <v>1100580.510791</v>
+        <v>1391720.594887</v>
       </c>
       <c r="N124" t="n">
-        <v>1141767.528638</v>
+        <v>1426452.511204</v>
       </c>
       <c r="O124" t="n">
-        <v>1174791.239641</v>
+        <v>1451601.123885</v>
       </c>
       <c r="P124" t="n">
-        <v>1203918.88596</v>
+        <v>1472972.56965</v>
       </c>
       <c r="Q124" t="n">
-        <v>1231886.851687</v>
+        <v>1493614.144769</v>
       </c>
       <c r="R124" t="n">
-        <v>1254421.442162</v>
+        <v>1508029.665015</v>
       </c>
       <c r="S124" t="n">
-        <v>1272316.925928</v>
+        <v>1517331.948879</v>
       </c>
       <c r="T124" t="n">
-        <v>1285966.661671</v>
+        <v>1521475.852731</v>
       </c>
       <c r="U124" t="n">
-        <v>1294576.553168</v>
+        <v>1520071.442615</v>
       </c>
       <c r="V124" t="n">
-        <v>1297850.589957</v>
+        <v>1513603.935666</v>
       </c>
     </row>
     <row r="125">
@@ -9874,58 +9874,58 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>1260072.612924</v>
+        <v>955746.748505</v>
       </c>
       <c r="F125" t="n">
-        <v>1269106.50951</v>
+        <v>943783.401864</v>
       </c>
       <c r="G125" t="n">
-        <v>1304747.347483</v>
+        <v>943926.024425</v>
       </c>
       <c r="H125" t="n">
-        <v>1319876.005508</v>
+        <v>938722.51541</v>
       </c>
       <c r="I125" t="n">
-        <v>1331236.493024</v>
+        <v>940284.117948</v>
       </c>
       <c r="J125" t="n">
-        <v>1351179.821804</v>
+        <v>955256.325205</v>
       </c>
       <c r="K125" t="n">
-        <v>1374230.887563</v>
+        <v>976824.623809</v>
       </c>
       <c r="L125" t="n">
-        <v>1392254.384052</v>
+        <v>996998.736184</v>
       </c>
       <c r="M125" t="n">
-        <v>1413028.716089</v>
+        <v>1019637.48869</v>
       </c>
       <c r="N125" t="n">
-        <v>1430918.179206</v>
+        <v>1039769.630687</v>
       </c>
       <c r="O125" t="n">
-        <v>1437571.621792</v>
+        <v>1050874.942777</v>
       </c>
       <c r="P125" t="n">
-        <v>1439815.425211</v>
+        <v>1058065.528365</v>
       </c>
       <c r="Q125" t="n">
-        <v>1441163.002719</v>
+        <v>1064471.700145</v>
       </c>
       <c r="R125" t="n">
-        <v>1436738.046781</v>
+        <v>1066910.643802</v>
       </c>
       <c r="S125" t="n">
-        <v>1427821.138098</v>
+        <v>1066206.724787</v>
       </c>
       <c r="T125" t="n">
-        <v>1412692.0752</v>
+        <v>1061046.989398</v>
       </c>
       <c r="U125" t="n">
-        <v>1391738.360856</v>
+        <v>1051302.730777</v>
       </c>
       <c r="V125" t="n">
-        <v>1367659.22951</v>
+        <v>1038866.259367</v>
       </c>
     </row>
     <row r="126">
@@ -14130,55 +14130,55 @@
         </is>
       </c>
       <c r="E181" t="n">
+        <v>-7e-06</v>
+      </c>
+      <c r="F181" t="n">
         <v>-6e-06</v>
       </c>
-      <c r="F181" t="n">
-        <v>-9e-06</v>
-      </c>
       <c r="G181" t="n">
-        <v>-1e-06</v>
+        <v>-2e-06</v>
       </c>
       <c r="H181" t="n">
-        <v>2e-06</v>
+        <v>6e-06</v>
       </c>
       <c r="I181" t="n">
         <v>-5e-06</v>
       </c>
       <c r="J181" t="n">
-        <v>1e-06</v>
+        <v>-3e-06</v>
       </c>
       <c r="K181" t="n">
         <v>4e-06</v>
       </c>
       <c r="L181" t="n">
-        <v>-2e-06</v>
+        <v>-3e-06</v>
       </c>
       <c r="M181" t="n">
+        <v>4e-06</v>
+      </c>
+      <c r="N181" t="n">
+        <v>-5e-06</v>
+      </c>
+      <c r="O181" t="n">
+        <v>3e-06</v>
+      </c>
+      <c r="P181" t="n">
         <v>2e-06</v>
       </c>
-      <c r="N181" t="n">
+      <c r="Q181" t="n">
         <v>-6e-06</v>
       </c>
-      <c r="O181" t="n">
-        <v>4e-06</v>
-      </c>
-      <c r="P181" t="n">
-        <v>1e-06</v>
-      </c>
-      <c r="Q181" t="n">
-        <v>-5e-06</v>
-      </c>
       <c r="R181" t="n">
+        <v>5e-06</v>
+      </c>
+      <c r="S181" t="n">
         <v>3e-06</v>
-      </c>
-      <c r="S181" t="n">
-        <v>4e-06</v>
       </c>
       <c r="T181" t="n">
         <v>-5e-06</v>
       </c>
       <c r="U181" t="n">
-        <v>-2e-06</v>
+        <v>-3e-06</v>
       </c>
       <c r="V181" t="n">
         <v>-2e-06</v>
